--- a/photography_forms/010_newborn_photography_survey--photography_forms.xlsx
+++ b/photography_forms/010_newborn_photography_survey--photography_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Studio Policy</t>
+          <t>Studio Policy Consent Time</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Studio Policy</t>
+          <t>Studio Policy Consent Length</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Studio Policy</t>
+          <t>Studio Policy Consent</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -776,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>i_agree</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>I agree</t>
         </is>
       </c>
     </row>
@@ -928,29 +928,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>i_do_not_agree</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>I do not agree</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>studio_policy_consent_choices</t>
+          <t>studio_policy_consent_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -979,29 +979,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>studio_policy_consent_2_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
